--- a/Mentorias/2026-09-16_Emerson_e_Julio/10_Prever_volatilidade.xlsx
+++ b/Mentorias/2026-09-16_Emerson_e_Julio/10_Prever_volatilidade.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A resposta" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por que falhou antes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="O alvo certo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Em porcentagem" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A resposta" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por que falhou antes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="O alvo certo" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,6 +54,11 @@
       <b val="1"/>
       <color rgb="00006100"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -128,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -146,19 +152,20 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -524,6 +531,426 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>A NOTÍCIA MOVE O PREÇO? EM QUANTO POR CENTO?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>PETR4 · excesso sobre 618 noites em que não houve nada (nem notícia acima do normal, nem comunicado à CVM) · * = passa no teste estatístico</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>O que aconteceu na noite</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Noites</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Volatilidade</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Tamanho da variação</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>muita notícia, sem CVM</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>449</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>-3,5%</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>-0,6%</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>-5,0% *</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Comunicado ao Mercado</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>828</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>-0,5%</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>-1,3%</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>-1,1% *</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Fato Relevante</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+6,4%</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>+18,9% *</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>+11,9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>FATO RELEVANTE + muita notícia</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+13,2% *</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>+38,2% *</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>+19,4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>A NOTÍCIA SOZINHA NÃO MOVE. O COMUNICADO SOZINHO NÃO MOVE. OS DOIS JUNTOS MOVEM +38%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>O MESMO, EM NÚMEROS DO DIA A DIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Tipo de noite</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Quanto a ação oscila</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Quanto gira</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>noite em que não houve nada</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>1.31%</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>46.3 milhões de ações</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>noite de muita notícia (sem CVM)</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>1.30%</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>44.2 milhões de ações</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>noite de FATO RELEVANTE</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>1.65%</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>60.4 milhões de ações</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>FATO RELEVANTE + muita notícia</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>1.70%</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>62.5 milhões de ações</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>E A DIREÇÃO? CONTINUA IMPREVISÍVEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Tom da noite</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Noites</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Retorno médio no dia seguinte</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>% de alta</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>noite de tom MUITO NEGATIVO</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>-0.170%</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>46.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>noite de tom comum</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>1.157</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>+0.149%</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>noite de tom MUITO POSITIVO</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>+0.164%</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>53.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>diferença entre o tom muito negativo e o muito positivo: p = 0.291 — NÃO PASSA. Parece certo, mas pode ser sorte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>CUIDADO AO APRESENTAR — por que estes números diferem do Artigo 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>O Artigo 1 relata +9,6% de volatilidade. Não há contradição:</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · o artigo mede 54 papéis contra 105.896 pregões sem evento algum;</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · esta aba mede só a PETR4, contra um controle que JÁ EXCLUI as</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    noites de notícia — um adversário mais duro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Escopos diferentes, perguntas diferentes, ambos corretos.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -683,48 +1110,48 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>O comunicado à CVM avisa que houve um fato de verdade.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>O volume de notícias avisa que o mercado reparou nele.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr"/>
+      <c r="A14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Fato que ninguém comentou não move o preço.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Comentário sem fato também não.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>É o encontro dos dois que antecede o dia agitado.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr"/>
+      <c r="A18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>valor-p da combinação: 0.00015</t>
         </is>
@@ -739,7 +1166,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -784,117 +1211,117 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>só notícia: quantidade</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>51.8%</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>55.8%</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>-4.02 pts</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>só notícia: intensidade do tom</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>51.9%</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>55.4%</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>-3.49 pts</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>notícia: quantidade + intensidade</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>51.3%</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>55.6%</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>-4.35 pts</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>notícia + houve comunicado</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>50.7%</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>55.6%</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>-4.96 pts</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>notícia + Fato Relevante</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>51.1%</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>55.6%</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>-4.54 pts</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>A EXPLICAÇÃO</t>
         </is>
@@ -941,107 +1368,107 @@
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>percentil 75</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>1.238</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>1.345</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>+8.6%</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>percentil 90</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>1.640</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>1.834</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>+11.8%</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>os dias agitados (perc. 95)</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>1.922</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>2.298</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>+19.6%  (muito)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>O Fato Relevante mexe na PONTA da distribuição, não no meio.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr"/>
+      <c r="A22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>A analogia: é como uma cidade que ganha alguns prédios muito altos.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>A altura média sobe, mas a casa típica continua igual.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>Quem perguntar 'a casa da esquina é mais alta que a média?' não nota nada.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr"/>
+      <c r="A26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>Era isso que a minha pergunta fazia: olhava o meio, e o efeito estava na ponta.</t>
         </is>
@@ -1055,7 +1482,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1209,55 +1636,55 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>ISTO NÃO FOI PESCARIA.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr"/>
+      <c r="A11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>A tese do efeito de cauda, sustentada desde a primeira auditoria,</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>prevê exatamente que o sinal esteja no extremo e não no centro.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Testá-la é obrigação, não conveniência.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr"/>
+      <c r="A15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Ainda assim: três alvos foram testados (acima/abaixo, topo 10%, topo 5%).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>No topo 5% a direção se mantém, mas caem para 22 os casos e o</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>resultado perde significância. Quem lê tem direito de saber disso.</t>
         </is>
